--- a/RangeSayacv3_yeni_taslakv2.xlsx
+++ b/RangeSayacv3_yeni_taslakv2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaank\Downloads\IpekyolRangeSayac\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B7C469B-8AE7-4852-AEE8-80021A23BDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A03FED7-48AA-4BBF-A43D-C59A3FA0B066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sayfa2" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$J$537</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3390,6 +3390,9 @@
       <c r="E70" s="15" t="s">
         <v>173</v>
       </c>
+      <c r="F70">
+        <v>1458</v>
+      </c>
       <c r="G70" s="13" t="s">
         <v>4</v>
       </c>
@@ -3417,6 +3420,9 @@
       <c r="E71" s="15" t="s">
         <v>173</v>
       </c>
+      <c r="F71">
+        <v>1458</v>
+      </c>
       <c r="G71" s="14" t="s">
         <v>144</v>
       </c>
@@ -3444,6 +3450,9 @@
       <c r="E72" s="15" t="s">
         <v>173</v>
       </c>
+      <c r="F72">
+        <v>1458</v>
+      </c>
       <c r="G72" s="14" t="s">
         <v>5</v>
       </c>
@@ -3471,6 +3480,9 @@
       <c r="E73" s="15" t="s">
         <v>173</v>
       </c>
+      <c r="F73">
+        <v>1458</v>
+      </c>
       <c r="G73" s="14" t="s">
         <v>6</v>
       </c>
@@ -3498,6 +3510,9 @@
       <c r="E74" s="15" t="s">
         <v>173</v>
       </c>
+      <c r="F74">
+        <v>1458</v>
+      </c>
       <c r="G74" s="14" t="s">
         <v>7</v>
       </c>
@@ -3525,6 +3540,9 @@
       <c r="E75" s="15" t="s">
         <v>173</v>
       </c>
+      <c r="F75">
+        <v>1458</v>
+      </c>
       <c r="G75" s="14" t="s">
         <v>8</v>
       </c>
@@ -3552,6 +3570,9 @@
       <c r="E76" s="15" t="s">
         <v>173</v>
       </c>
+      <c r="F76">
+        <v>1458</v>
+      </c>
       <c r="G76" s="14" t="s">
         <v>9</v>
       </c>
@@ -3581,6 +3602,9 @@
       <c r="E77" s="15" t="s">
         <v>173</v>
       </c>
+      <c r="F77">
+        <v>1458</v>
+      </c>
       <c r="G77" s="14" t="s">
         <v>11</v>
       </c>
@@ -3608,6 +3632,9 @@
       <c r="E78" s="15" t="s">
         <v>173</v>
       </c>
+      <c r="F78">
+        <v>1458</v>
+      </c>
       <c r="G78" s="14" t="s">
         <v>12</v>
       </c>
@@ -3635,6 +3662,9 @@
       <c r="E79" s="15" t="s">
         <v>173</v>
       </c>
+      <c r="F79">
+        <v>1458</v>
+      </c>
       <c r="G79" s="14" t="s">
         <v>55</v>
       </c>
@@ -3662,6 +3692,9 @@
       <c r="E80" s="15" t="s">
         <v>173</v>
       </c>
+      <c r="F80">
+        <v>1458</v>
+      </c>
       <c r="G80" s="14" t="s">
         <v>167</v>
       </c>
@@ -3689,6 +3722,9 @@
       <c r="E81" s="15" t="s">
         <v>173</v>
       </c>
+      <c r="F81">
+        <v>1458</v>
+      </c>
       <c r="G81" s="14" t="s">
         <v>14</v>
       </c>
@@ -3716,6 +3752,9 @@
       <c r="E82" s="15" t="s">
         <v>173</v>
       </c>
+      <c r="F82">
+        <v>1458</v>
+      </c>
       <c r="G82" s="14" t="s">
         <v>169</v>
       </c>
@@ -3743,6 +3782,9 @@
       <c r="E83" s="15" t="s">
         <v>173</v>
       </c>
+      <c r="F83">
+        <v>1458</v>
+      </c>
       <c r="G83" s="14" t="s">
         <v>15</v>
       </c>
@@ -3770,6 +3812,9 @@
       <c r="E84" s="15" t="s">
         <v>173</v>
       </c>
+      <c r="F84">
+        <v>1458</v>
+      </c>
       <c r="G84" s="14" t="s">
         <v>16</v>
       </c>
@@ -3797,6 +3842,9 @@
       <c r="E85" s="15" t="s">
         <v>173</v>
       </c>
+      <c r="F85">
+        <v>1458</v>
+      </c>
       <c r="G85" s="14" t="s">
         <v>17</v>
       </c>
@@ -3824,6 +3872,9 @@
       <c r="E86" s="15" t="s">
         <v>173</v>
       </c>
+      <c r="F86">
+        <v>1458</v>
+      </c>
       <c r="G86" s="14" t="s">
         <v>18</v>
       </c>
@@ -5975,6 +6026,9 @@
       <c r="E155" s="16" t="s">
         <v>174</v>
       </c>
+      <c r="F155">
+        <v>1459</v>
+      </c>
       <c r="G155" s="13" t="s">
         <v>4</v>
       </c>
@@ -6002,6 +6056,9 @@
       <c r="E156" s="16" t="s">
         <v>174</v>
       </c>
+      <c r="F156">
+        <v>1459</v>
+      </c>
       <c r="G156" s="14" t="s">
         <v>144</v>
       </c>
@@ -6031,6 +6088,9 @@
       <c r="E157" s="16" t="s">
         <v>174</v>
       </c>
+      <c r="F157">
+        <v>1459</v>
+      </c>
       <c r="G157" s="14" t="s">
         <v>5</v>
       </c>
@@ -6060,6 +6120,9 @@
       <c r="E158" s="16" t="s">
         <v>174</v>
       </c>
+      <c r="F158">
+        <v>1459</v>
+      </c>
       <c r="G158" s="14" t="s">
         <v>6</v>
       </c>
@@ -6089,6 +6152,9 @@
       <c r="E159" s="16" t="s">
         <v>174</v>
       </c>
+      <c r="F159">
+        <v>1459</v>
+      </c>
       <c r="G159" s="14" t="s">
         <v>7</v>
       </c>
@@ -6118,6 +6184,9 @@
       <c r="E160" s="16" t="s">
         <v>174</v>
       </c>
+      <c r="F160">
+        <v>1459</v>
+      </c>
       <c r="G160" s="14" t="s">
         <v>8</v>
       </c>
@@ -6145,6 +6214,9 @@
       <c r="E161" s="16" t="s">
         <v>174</v>
       </c>
+      <c r="F161">
+        <v>1459</v>
+      </c>
       <c r="G161" s="14" t="s">
         <v>9</v>
       </c>
@@ -6172,6 +6244,9 @@
       <c r="E162" s="16" t="s">
         <v>174</v>
       </c>
+      <c r="F162">
+        <v>1459</v>
+      </c>
       <c r="G162" s="14" t="s">
         <v>11</v>
       </c>
@@ -6199,6 +6274,9 @@
       <c r="E163" s="16" t="s">
         <v>174</v>
       </c>
+      <c r="F163">
+        <v>1459</v>
+      </c>
       <c r="G163" s="14" t="s">
         <v>12</v>
       </c>
@@ -6228,6 +6306,9 @@
       <c r="E164" s="16" t="s">
         <v>174</v>
       </c>
+      <c r="F164">
+        <v>1459</v>
+      </c>
       <c r="G164" s="14" t="s">
         <v>55</v>
       </c>
@@ -6255,6 +6336,9 @@
       <c r="E165" s="16" t="s">
         <v>174</v>
       </c>
+      <c r="F165">
+        <v>1459</v>
+      </c>
       <c r="G165" s="14" t="s">
         <v>167</v>
       </c>
@@ -6284,6 +6368,9 @@
       <c r="E166" s="16" t="s">
         <v>174</v>
       </c>
+      <c r="F166">
+        <v>1459</v>
+      </c>
       <c r="G166" s="14" t="s">
         <v>14</v>
       </c>
@@ -6313,6 +6400,9 @@
       <c r="E167" s="16" t="s">
         <v>174</v>
       </c>
+      <c r="F167">
+        <v>1459</v>
+      </c>
       <c r="G167" s="14" t="s">
         <v>169</v>
       </c>
@@ -6342,6 +6432,9 @@
       <c r="E168" s="16" t="s">
         <v>174</v>
       </c>
+      <c r="F168">
+        <v>1459</v>
+      </c>
       <c r="G168" s="14" t="s">
         <v>15</v>
       </c>
@@ -6371,6 +6464,9 @@
       <c r="E169" s="16" t="s">
         <v>174</v>
       </c>
+      <c r="F169">
+        <v>1459</v>
+      </c>
       <c r="G169" s="14" t="s">
         <v>16</v>
       </c>
@@ -6398,6 +6494,9 @@
       <c r="E170" s="16" t="s">
         <v>174</v>
       </c>
+      <c r="F170">
+        <v>1459</v>
+      </c>
       <c r="G170" s="14" t="s">
         <v>17</v>
       </c>
@@ -6427,6 +6526,9 @@
       <c r="E171" s="16" t="s">
         <v>174</v>
       </c>
+      <c r="F171">
+        <v>1459</v>
+      </c>
       <c r="G171" s="14" t="s">
         <v>18</v>
       </c>
@@ -7508,6 +7610,9 @@
       <c r="E206" s="17" t="s">
         <v>77</v>
       </c>
+      <c r="F206">
+        <v>1457</v>
+      </c>
       <c r="G206" s="13" t="s">
         <v>4</v>
       </c>
@@ -7535,6 +7640,9 @@
       <c r="E207" s="17" t="s">
         <v>77</v>
       </c>
+      <c r="F207">
+        <v>1457</v>
+      </c>
       <c r="G207" s="14" t="s">
         <v>144</v>
       </c>
@@ -7562,6 +7670,9 @@
       <c r="E208" s="17" t="s">
         <v>77</v>
       </c>
+      <c r="F208">
+        <v>1457</v>
+      </c>
       <c r="G208" s="14" t="s">
         <v>5</v>
       </c>
@@ -7591,6 +7702,9 @@
       <c r="E209" s="17" t="s">
         <v>77</v>
       </c>
+      <c r="F209">
+        <v>1457</v>
+      </c>
       <c r="G209" s="14" t="s">
         <v>6</v>
       </c>
@@ -7620,6 +7734,9 @@
       <c r="E210" s="17" t="s">
         <v>77</v>
       </c>
+      <c r="F210">
+        <v>1457</v>
+      </c>
       <c r="G210" s="14" t="s">
         <v>7</v>
       </c>
@@ -7649,6 +7766,9 @@
       <c r="E211" s="17" t="s">
         <v>77</v>
       </c>
+      <c r="F211">
+        <v>1457</v>
+      </c>
       <c r="G211" s="14" t="s">
         <v>8</v>
       </c>
@@ -7678,6 +7798,9 @@
       <c r="E212" s="17" t="s">
         <v>77</v>
       </c>
+      <c r="F212">
+        <v>1457</v>
+      </c>
       <c r="G212" s="14" t="s">
         <v>9</v>
       </c>
@@ -7705,6 +7828,9 @@
       <c r="E213" s="17" t="s">
         <v>77</v>
       </c>
+      <c r="F213">
+        <v>1457</v>
+      </c>
       <c r="G213" s="14" t="s">
         <v>11</v>
       </c>
@@ -7732,6 +7858,9 @@
       <c r="E214" s="17" t="s">
         <v>77</v>
       </c>
+      <c r="F214">
+        <v>1457</v>
+      </c>
       <c r="G214" s="14" t="s">
         <v>12</v>
       </c>
@@ -7761,6 +7890,9 @@
       <c r="E215" s="17" t="s">
         <v>77</v>
       </c>
+      <c r="F215">
+        <v>1457</v>
+      </c>
       <c r="G215" s="14" t="s">
         <v>55</v>
       </c>
@@ -7788,6 +7920,9 @@
       <c r="E216" s="17" t="s">
         <v>77</v>
       </c>
+      <c r="F216">
+        <v>1457</v>
+      </c>
       <c r="G216" s="14" t="s">
         <v>167</v>
       </c>
@@ -7815,6 +7950,9 @@
       <c r="E217" s="17" t="s">
         <v>77</v>
       </c>
+      <c r="F217">
+        <v>1457</v>
+      </c>
       <c r="G217" s="14" t="s">
         <v>14</v>
       </c>
@@ -7844,6 +7982,9 @@
       <c r="E218" s="17" t="s">
         <v>77</v>
       </c>
+      <c r="F218">
+        <v>1457</v>
+      </c>
       <c r="G218" s="14" t="s">
         <v>169</v>
       </c>
@@ -7871,6 +8012,9 @@
       <c r="E219" s="17" t="s">
         <v>77</v>
       </c>
+      <c r="F219">
+        <v>1457</v>
+      </c>
       <c r="G219" s="14" t="s">
         <v>15</v>
       </c>
@@ -7900,6 +8044,9 @@
       <c r="E220" s="17" t="s">
         <v>77</v>
       </c>
+      <c r="F220">
+        <v>1457</v>
+      </c>
       <c r="G220" s="14" t="s">
         <v>16</v>
       </c>
@@ -7929,6 +8076,9 @@
       <c r="E221" s="17" t="s">
         <v>77</v>
       </c>
+      <c r="F221">
+        <v>1457</v>
+      </c>
       <c r="G221" s="14" t="s">
         <v>17</v>
       </c>
@@ -7956,6 +8106,9 @@
       <c r="E222" s="17" t="s">
         <v>77</v>
       </c>
+      <c r="F222">
+        <v>1457</v>
+      </c>
       <c r="G222" s="14" t="s">
         <v>18</v>
       </c>
@@ -7992,7 +8145,7 @@
         <v>4</v>
       </c>
       <c r="H223" s="20">
-        <f>VLOOKUP(G223,$G$1:$H$222,2,0)</f>
+        <f t="shared" ref="H223:H286" si="0">VLOOKUP(G223,$G$1:$H$222,2,0)</f>
         <v>21</v>
       </c>
       <c r="I223" s="21"/>
@@ -8023,7 +8176,7 @@
         <v>5</v>
       </c>
       <c r="H224" s="20">
-        <f>VLOOKUP(G224,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="I224" s="23">
@@ -8056,7 +8209,7 @@
         <v>6</v>
       </c>
       <c r="H225" s="20">
-        <f>VLOOKUP(G225,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="I225" s="23">
@@ -8089,7 +8242,7 @@
         <v>7</v>
       </c>
       <c r="H226" s="20">
-        <f>VLOOKUP(G226,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I226" s="23">
@@ -8122,7 +8275,7 @@
         <v>8</v>
       </c>
       <c r="H227" s="20">
-        <f>VLOOKUP(G227,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="I227" s="23">
@@ -8155,7 +8308,7 @@
         <v>9</v>
       </c>
       <c r="H228" s="20">
-        <f>VLOOKUP(G228,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="I228" s="23"/>
@@ -8186,7 +8339,7 @@
         <v>11</v>
       </c>
       <c r="H229" s="20">
-        <f>VLOOKUP(G229,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="I229" s="23">
@@ -8219,7 +8372,7 @@
         <v>12</v>
       </c>
       <c r="H230" s="20">
-        <f>VLOOKUP(G230,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="I230" s="23">
@@ -8252,7 +8405,7 @@
         <v>55</v>
       </c>
       <c r="H231" s="20">
-        <f>VLOOKUP(G231,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="I231" s="23">
@@ -8285,7 +8438,7 @@
         <v>167</v>
       </c>
       <c r="H232" s="20">
-        <f>VLOOKUP(G232,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="I232" s="23"/>
@@ -8316,7 +8469,7 @@
         <v>14</v>
       </c>
       <c r="H233" s="20">
-        <f>VLOOKUP(G233,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="I233" s="23">
@@ -8349,7 +8502,7 @@
         <v>15</v>
       </c>
       <c r="H234" s="20">
-        <f>VLOOKUP(G234,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="I234" s="23">
@@ -8382,7 +8535,7 @@
         <v>16</v>
       </c>
       <c r="H235" s="20">
-        <f>VLOOKUP(G235,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="I235" s="23">
@@ -8415,7 +8568,7 @@
         <v>17</v>
       </c>
       <c r="H236" s="20">
-        <f>VLOOKUP(G236,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="I236" s="23"/>
@@ -8446,7 +8599,7 @@
         <v>18</v>
       </c>
       <c r="H237" s="20">
-        <f>VLOOKUP(G237,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="I237" s="24"/>
@@ -8477,7 +8630,7 @@
         <v>4</v>
       </c>
       <c r="H238" s="20">
-        <f>VLOOKUP(G238,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="I238" s="21"/>
@@ -8508,7 +8661,7 @@
         <v>5</v>
       </c>
       <c r="H239" s="20">
-        <f>VLOOKUP(G239,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="I239" s="23">
@@ -8541,7 +8694,7 @@
         <v>6</v>
       </c>
       <c r="H240" s="20">
-        <f>VLOOKUP(G240,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="I240" s="23"/>
@@ -8572,7 +8725,7 @@
         <v>7</v>
       </c>
       <c r="H241" s="20">
-        <f>VLOOKUP(G241,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I241" s="23"/>
@@ -8603,7 +8756,7 @@
         <v>8</v>
       </c>
       <c r="H242" s="20">
-        <f>VLOOKUP(G242,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="I242" s="23">
@@ -8636,7 +8789,7 @@
         <v>9</v>
       </c>
       <c r="H243" s="20">
-        <f>VLOOKUP(G243,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="I243" s="23"/>
@@ -8667,7 +8820,7 @@
         <v>11</v>
       </c>
       <c r="H244" s="20">
-        <f>VLOOKUP(G244,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="I244" s="23">
@@ -8700,7 +8853,7 @@
         <v>12</v>
       </c>
       <c r="H245" s="20">
-        <f>VLOOKUP(G245,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="I245" s="23">
@@ -8733,7 +8886,7 @@
         <v>55</v>
       </c>
       <c r="H246" s="20">
-        <f>VLOOKUP(G246,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="I246" s="23">
@@ -8766,7 +8919,7 @@
         <v>167</v>
       </c>
       <c r="H247" s="20">
-        <f>VLOOKUP(G247,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="I247" s="23"/>
@@ -8797,7 +8950,7 @@
         <v>14</v>
       </c>
       <c r="H248" s="20">
-        <f>VLOOKUP(G248,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="I248" s="23">
@@ -8830,7 +8983,7 @@
         <v>15</v>
       </c>
       <c r="H249" s="20">
-        <f>VLOOKUP(G249,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="I249" s="23">
@@ -8863,7 +9016,7 @@
         <v>16</v>
       </c>
       <c r="H250" s="20">
-        <f>VLOOKUP(G250,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="I250" s="23">
@@ -8896,7 +9049,7 @@
         <v>17</v>
       </c>
       <c r="H251" s="20">
-        <f>VLOOKUP(G251,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="I251" s="23"/>
@@ -8927,7 +9080,7 @@
         <v>18</v>
       </c>
       <c r="H252" s="20">
-        <f>VLOOKUP(G252,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="I252" s="24"/>
@@ -8958,7 +9111,7 @@
         <v>4</v>
       </c>
       <c r="H253" s="20">
-        <f>VLOOKUP(G253,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="I253" s="21">
@@ -8991,7 +9144,7 @@
         <v>5</v>
       </c>
       <c r="H254" s="20">
-        <f>VLOOKUP(G254,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="I254" s="23">
@@ -9024,7 +9177,7 @@
         <v>6</v>
       </c>
       <c r="H255" s="20">
-        <f>VLOOKUP(G255,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="I255" s="23">
@@ -9057,7 +9210,7 @@
         <v>7</v>
       </c>
       <c r="H256" s="20">
-        <f>VLOOKUP(G256,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I256" s="23">
@@ -9090,7 +9243,7 @@
         <v>8</v>
       </c>
       <c r="H257" s="20">
-        <f>VLOOKUP(G257,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="I257" s="23">
@@ -9123,7 +9276,7 @@
         <v>9</v>
       </c>
       <c r="H258" s="20">
-        <f>VLOOKUP(G258,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="I258" s="23"/>
@@ -9154,7 +9307,7 @@
         <v>11</v>
       </c>
       <c r="H259" s="20">
-        <f>VLOOKUP(G259,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="I259" s="23">
@@ -9187,7 +9340,7 @@
         <v>12</v>
       </c>
       <c r="H260" s="20">
-        <f>VLOOKUP(G260,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="I260" s="23">
@@ -9220,7 +9373,7 @@
         <v>55</v>
       </c>
       <c r="H261" s="20">
-        <f>VLOOKUP(G261,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="I261" s="23"/>
@@ -9251,7 +9404,7 @@
         <v>167</v>
       </c>
       <c r="H262" s="20">
-        <f>VLOOKUP(G262,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="I262" s="23"/>
@@ -9282,7 +9435,7 @@
         <v>14</v>
       </c>
       <c r="H263" s="20">
-        <f>VLOOKUP(G263,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="I263" s="23">
@@ -9315,7 +9468,7 @@
         <v>15</v>
       </c>
       <c r="H264" s="20">
-        <f>VLOOKUP(G264,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="I264" s="23">
@@ -9348,7 +9501,7 @@
         <v>16</v>
       </c>
       <c r="H265" s="20">
-        <f>VLOOKUP(G265,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="I265" s="23">
@@ -9381,7 +9534,7 @@
         <v>17</v>
       </c>
       <c r="H266" s="20">
-        <f>VLOOKUP(G266,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="I266" s="23">
@@ -9414,7 +9567,7 @@
         <v>18</v>
       </c>
       <c r="H267" s="20">
-        <f>VLOOKUP(G267,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="I267" s="24"/>
@@ -9445,7 +9598,7 @@
         <v>4</v>
       </c>
       <c r="H268" s="20">
-        <f>VLOOKUP(G268,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="I268" s="21"/>
@@ -9476,7 +9629,7 @@
         <v>5</v>
       </c>
       <c r="H269" s="20">
-        <f>VLOOKUP(G269,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="I269" s="23">
@@ -9509,7 +9662,7 @@
         <v>6</v>
       </c>
       <c r="H270" s="20">
-        <f>VLOOKUP(G270,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="I270" s="23"/>
@@ -9540,7 +9693,7 @@
         <v>7</v>
       </c>
       <c r="H271" s="20">
-        <f>VLOOKUP(G271,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I271" s="23"/>
@@ -9571,7 +9724,7 @@
         <v>8</v>
       </c>
       <c r="H272" s="20">
-        <f>VLOOKUP(G272,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="I272" s="23">
@@ -9604,7 +9757,7 @@
         <v>9</v>
       </c>
       <c r="H273" s="20">
-        <f>VLOOKUP(G273,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="I273" s="23"/>
@@ -9635,7 +9788,7 @@
         <v>11</v>
       </c>
       <c r="H274" s="20">
-        <f>VLOOKUP(G274,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="I274" s="23">
@@ -9668,7 +9821,7 @@
         <v>12</v>
       </c>
       <c r="H275" s="20">
-        <f>VLOOKUP(G275,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="I275" s="23">
@@ -9701,7 +9854,7 @@
         <v>55</v>
       </c>
       <c r="H276" s="20">
-        <f>VLOOKUP(G276,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="I276" s="23">
@@ -9734,7 +9887,7 @@
         <v>167</v>
       </c>
       <c r="H277" s="20">
-        <f>VLOOKUP(G277,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="I277" s="23"/>
@@ -9765,7 +9918,7 @@
         <v>14</v>
       </c>
       <c r="H278" s="20">
-        <f>VLOOKUP(G278,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="I278" s="23"/>
@@ -9796,7 +9949,7 @@
         <v>15</v>
       </c>
       <c r="H279" s="20">
-        <f>VLOOKUP(G279,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="I279" s="23">
@@ -9829,7 +9982,7 @@
         <v>16</v>
       </c>
       <c r="H280" s="20">
-        <f>VLOOKUP(G280,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="I280" s="23">
@@ -9862,7 +10015,7 @@
         <v>17</v>
       </c>
       <c r="H281" s="20">
-        <f>VLOOKUP(G281,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="I281" s="23"/>
@@ -9893,7 +10046,7 @@
         <v>18</v>
       </c>
       <c r="H282" s="20">
-        <f>VLOOKUP(G282,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="I282" s="24"/>
@@ -9924,7 +10077,7 @@
         <v>4</v>
       </c>
       <c r="H283" s="20">
-        <f>VLOOKUP(G283,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="I283" s="21">
@@ -9957,7 +10110,7 @@
         <v>5</v>
       </c>
       <c r="H284" s="20">
-        <f>VLOOKUP(G284,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="I284" s="23">
@@ -9990,7 +10143,7 @@
         <v>6</v>
       </c>
       <c r="H285" s="20">
-        <f>VLOOKUP(G285,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="I285" s="23">
@@ -10023,7 +10176,7 @@
         <v>7</v>
       </c>
       <c r="H286" s="20">
-        <f>VLOOKUP(G286,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="I286" s="23">
@@ -10056,7 +10209,7 @@
         <v>8</v>
       </c>
       <c r="H287" s="20">
-        <f>VLOOKUP(G287,$G$1:$H$222,2,0)</f>
+        <f t="shared" ref="H287:H350" si="1">VLOOKUP(G287,$G$1:$H$222,2,0)</f>
         <v>49</v>
       </c>
       <c r="I287" s="23">
@@ -10089,7 +10242,7 @@
         <v>9</v>
       </c>
       <c r="H288" s="20">
-        <f>VLOOKUP(G288,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="I288" s="23"/>
@@ -10120,7 +10273,7 @@
         <v>11</v>
       </c>
       <c r="H289" s="20">
-        <f>VLOOKUP(G289,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="I289" s="23">
@@ -10153,7 +10306,7 @@
         <v>12</v>
       </c>
       <c r="H290" s="20">
-        <f>VLOOKUP(G290,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="I290" s="23">
@@ -10186,7 +10339,7 @@
         <v>55</v>
       </c>
       <c r="H291" s="20">
-        <f>VLOOKUP(G291,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="I291" s="23"/>
@@ -10217,7 +10370,7 @@
         <v>167</v>
       </c>
       <c r="H292" s="20">
-        <f>VLOOKUP(G292,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="I292" s="23"/>
@@ -10248,7 +10401,7 @@
         <v>14</v>
       </c>
       <c r="H293" s="20">
-        <f>VLOOKUP(G293,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="I293" s="23">
@@ -10281,7 +10434,7 @@
         <v>15</v>
       </c>
       <c r="H294" s="20">
-        <f>VLOOKUP(G294,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="I294" s="23">
@@ -10314,7 +10467,7 @@
         <v>16</v>
       </c>
       <c r="H295" s="20">
-        <f>VLOOKUP(G295,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="I295" s="23">
@@ -10347,7 +10500,7 @@
         <v>17</v>
       </c>
       <c r="H296" s="20">
-        <f>VLOOKUP(G296,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="I296" s="23">
@@ -10380,7 +10533,7 @@
         <v>18</v>
       </c>
       <c r="H297" s="20">
-        <f>VLOOKUP(G297,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="I297" s="24"/>
@@ -10411,7 +10564,7 @@
         <v>4</v>
       </c>
       <c r="H298" s="20">
-        <f>VLOOKUP(G298,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="I298" s="21"/>
@@ -10442,7 +10595,7 @@
         <v>5</v>
       </c>
       <c r="H299" s="20">
-        <f>VLOOKUP(G299,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="I299" s="23"/>
@@ -10473,7 +10626,7 @@
         <v>6</v>
       </c>
       <c r="H300" s="20">
-        <f>VLOOKUP(G300,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="I300" s="23"/>
@@ -10504,7 +10657,7 @@
         <v>7</v>
       </c>
       <c r="H301" s="20">
-        <f>VLOOKUP(G301,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I301" s="23"/>
@@ -10535,7 +10688,7 @@
         <v>8</v>
       </c>
       <c r="H302" s="20">
-        <f>VLOOKUP(G302,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="I302" s="23">
@@ -10568,7 +10721,7 @@
         <v>9</v>
       </c>
       <c r="H303" s="20">
-        <f>VLOOKUP(G303,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="I303" s="23"/>
@@ -10599,7 +10752,7 @@
         <v>11</v>
       </c>
       <c r="H304" s="20">
-        <f>VLOOKUP(G304,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="I304" s="23">
@@ -10632,7 +10785,7 @@
         <v>12</v>
       </c>
       <c r="H305" s="20">
-        <f>VLOOKUP(G305,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="I305" s="23">
@@ -10665,7 +10818,7 @@
         <v>55</v>
       </c>
       <c r="H306" s="20">
-        <f>VLOOKUP(G306,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="I306" s="23">
@@ -10698,7 +10851,7 @@
         <v>167</v>
       </c>
       <c r="H307" s="20">
-        <f>VLOOKUP(G307,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="I307" s="23"/>
@@ -10729,7 +10882,7 @@
         <v>14</v>
       </c>
       <c r="H308" s="20">
-        <f>VLOOKUP(G308,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="I308" s="23"/>
@@ -10760,7 +10913,7 @@
         <v>15</v>
       </c>
       <c r="H309" s="20">
-        <f>VLOOKUP(G309,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="I309" s="23">
@@ -10793,7 +10946,7 @@
         <v>16</v>
       </c>
       <c r="H310" s="20">
-        <f>VLOOKUP(G310,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="I310" s="23">
@@ -10826,7 +10979,7 @@
         <v>17</v>
       </c>
       <c r="H311" s="20">
-        <f>VLOOKUP(G311,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="I311" s="23"/>
@@ -10857,7 +11010,7 @@
         <v>18</v>
       </c>
       <c r="H312" s="20">
-        <f>VLOOKUP(G312,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="I312" s="24"/>
@@ -10888,7 +11041,7 @@
         <v>4</v>
       </c>
       <c r="H313" s="20">
-        <f>VLOOKUP(G313,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="I313" s="21"/>
@@ -10919,7 +11072,7 @@
         <v>5</v>
       </c>
       <c r="H314" s="20">
-        <f>VLOOKUP(G314,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="I314" s="23"/>
@@ -10950,7 +11103,7 @@
         <v>6</v>
       </c>
       <c r="H315" s="20">
-        <f>VLOOKUP(G315,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="I315" s="23"/>
@@ -10981,7 +11134,7 @@
         <v>7</v>
       </c>
       <c r="H316" s="20">
-        <f>VLOOKUP(G316,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I316" s="23"/>
@@ -11012,7 +11165,7 @@
         <v>8</v>
       </c>
       <c r="H317" s="20">
-        <f>VLOOKUP(G317,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="I317" s="23">
@@ -11045,7 +11198,7 @@
         <v>9</v>
       </c>
       <c r="H318" s="20">
-        <f>VLOOKUP(G318,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="I318" s="23"/>
@@ -11076,7 +11229,7 @@
         <v>11</v>
       </c>
       <c r="H319" s="20">
-        <f>VLOOKUP(G319,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="I319" s="23">
@@ -11109,7 +11262,7 @@
         <v>12</v>
       </c>
       <c r="H320" s="20">
-        <f>VLOOKUP(G320,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="I320" s="23">
@@ -11142,7 +11295,7 @@
         <v>55</v>
       </c>
       <c r="H321" s="20">
-        <f>VLOOKUP(G321,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="I321" s="23">
@@ -11175,7 +11328,7 @@
         <v>167</v>
       </c>
       <c r="H322" s="20">
-        <f>VLOOKUP(G322,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="I322" s="23"/>
@@ -11206,7 +11359,7 @@
         <v>14</v>
       </c>
       <c r="H323" s="20">
-        <f>VLOOKUP(G323,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="I323" s="23">
@@ -11239,7 +11392,7 @@
         <v>15</v>
       </c>
       <c r="H324" s="20">
-        <f>VLOOKUP(G324,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="I324" s="23">
@@ -11272,7 +11425,7 @@
         <v>16</v>
       </c>
       <c r="H325" s="20">
-        <f>VLOOKUP(G325,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="I325" s="23">
@@ -11305,7 +11458,7 @@
         <v>17</v>
       </c>
       <c r="H326" s="20">
-        <f>VLOOKUP(G326,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="I326" s="23"/>
@@ -11336,7 +11489,7 @@
         <v>18</v>
       </c>
       <c r="H327" s="20">
-        <f>VLOOKUP(G327,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="I327" s="24"/>
@@ -11360,11 +11513,14 @@
       <c r="E328" s="27" t="s">
         <v>176</v>
       </c>
+      <c r="F328">
+        <v>1452</v>
+      </c>
       <c r="G328" s="19" t="s">
         <v>4</v>
       </c>
       <c r="H328" s="20">
-        <f>VLOOKUP(G328,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="I328" s="21">
@@ -11390,11 +11546,14 @@
       <c r="E329" s="27" t="s">
         <v>176</v>
       </c>
+      <c r="F329">
+        <v>1452</v>
+      </c>
       <c r="G329" s="22" t="s">
         <v>5</v>
       </c>
       <c r="H329" s="20">
-        <f>VLOOKUP(G329,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="I329" s="23">
@@ -11420,11 +11579,14 @@
       <c r="E330" s="27" t="s">
         <v>176</v>
       </c>
+      <c r="F330">
+        <v>1452</v>
+      </c>
       <c r="G330" s="22" t="s">
         <v>6</v>
       </c>
       <c r="H330" s="20">
-        <f>VLOOKUP(G330,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="I330" s="23"/>
@@ -11448,11 +11610,14 @@
       <c r="E331" s="27" t="s">
         <v>176</v>
       </c>
+      <c r="F331">
+        <v>1452</v>
+      </c>
       <c r="G331" s="22" t="s">
         <v>7</v>
       </c>
       <c r="H331" s="20">
-        <f>VLOOKUP(G331,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I331" s="23"/>
@@ -11476,11 +11641,14 @@
       <c r="E332" s="27" t="s">
         <v>176</v>
       </c>
+      <c r="F332">
+        <v>1452</v>
+      </c>
       <c r="G332" s="22" t="s">
         <v>8</v>
       </c>
       <c r="H332" s="20">
-        <f>VLOOKUP(G332,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="I332" s="23">
@@ -11506,11 +11674,14 @@
       <c r="E333" s="27" t="s">
         <v>176</v>
       </c>
+      <c r="F333">
+        <v>1452</v>
+      </c>
       <c r="G333" s="22" t="s">
         <v>9</v>
       </c>
       <c r="H333" s="20">
-        <f>VLOOKUP(G333,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="I333" s="23"/>
@@ -11534,11 +11705,14 @@
       <c r="E334" s="27" t="s">
         <v>176</v>
       </c>
+      <c r="F334">
+        <v>1452</v>
+      </c>
       <c r="G334" s="22" t="s">
         <v>11</v>
       </c>
       <c r="H334" s="20">
-        <f>VLOOKUP(G334,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="I334" s="23"/>
@@ -11562,11 +11736,14 @@
       <c r="E335" s="27" t="s">
         <v>176</v>
       </c>
+      <c r="F335">
+        <v>1452</v>
+      </c>
       <c r="G335" s="22" t="s">
         <v>12</v>
       </c>
       <c r="H335" s="20">
-        <f>VLOOKUP(G335,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="I335" s="23">
@@ -11592,11 +11769,14 @@
       <c r="E336" s="27" t="s">
         <v>176</v>
       </c>
+      <c r="F336">
+        <v>1452</v>
+      </c>
       <c r="G336" s="22" t="s">
         <v>55</v>
       </c>
       <c r="H336" s="20">
-        <f>VLOOKUP(G336,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="I336" s="23"/>
@@ -11620,11 +11800,14 @@
       <c r="E337" s="27" t="s">
         <v>176</v>
       </c>
+      <c r="F337">
+        <v>1452</v>
+      </c>
       <c r="G337" s="22" t="s">
         <v>167</v>
       </c>
       <c r="H337" s="20">
-        <f>VLOOKUP(G337,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="I337" s="23"/>
@@ -11648,11 +11831,14 @@
       <c r="E338" s="27" t="s">
         <v>176</v>
       </c>
+      <c r="F338">
+        <v>1452</v>
+      </c>
       <c r="G338" s="22" t="s">
         <v>14</v>
       </c>
       <c r="H338" s="20">
-        <f>VLOOKUP(G338,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="I338" s="23">
@@ -11678,11 +11864,14 @@
       <c r="E339" s="27" t="s">
         <v>176</v>
       </c>
+      <c r="F339">
+        <v>1452</v>
+      </c>
       <c r="G339" s="22" t="s">
         <v>15</v>
       </c>
       <c r="H339" s="20">
-        <f>VLOOKUP(G339,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="I339" s="23">
@@ -11708,11 +11897,14 @@
       <c r="E340" s="27" t="s">
         <v>176</v>
       </c>
+      <c r="F340">
+        <v>1452</v>
+      </c>
       <c r="G340" s="22" t="s">
         <v>16</v>
       </c>
       <c r="H340" s="20">
-        <f>VLOOKUP(G340,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="I340" s="23"/>
@@ -11736,11 +11928,14 @@
       <c r="E341" s="27" t="s">
         <v>176</v>
       </c>
+      <c r="F341">
+        <v>1452</v>
+      </c>
       <c r="G341" s="22" t="s">
         <v>17</v>
       </c>
       <c r="H341" s="20">
-        <f>VLOOKUP(G341,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="I341" s="23"/>
@@ -11764,11 +11959,14 @@
       <c r="E342" s="27" t="s">
         <v>176</v>
       </c>
+      <c r="F342">
+        <v>1452</v>
+      </c>
       <c r="G342" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H342" s="20">
-        <f>VLOOKUP(G342,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="I342" s="24"/>
@@ -11799,7 +11997,7 @@
         <v>4</v>
       </c>
       <c r="H343" s="20">
-        <f>VLOOKUP(G343,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="I343" s="21">
@@ -11832,7 +12030,7 @@
         <v>5</v>
       </c>
       <c r="H344" s="20">
-        <f>VLOOKUP(G344,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="I344" s="23">
@@ -11865,7 +12063,7 @@
         <v>6</v>
       </c>
       <c r="H345" s="20">
-        <f>VLOOKUP(G345,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="I345" s="23">
@@ -11898,7 +12096,7 @@
         <v>7</v>
       </c>
       <c r="H346" s="20">
-        <f>VLOOKUP(G346,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="I346" s="23">
@@ -11931,7 +12129,7 @@
         <v>8</v>
       </c>
       <c r="H347" s="20">
-        <f>VLOOKUP(G347,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="I347" s="23">
@@ -11964,7 +12162,7 @@
         <v>9</v>
       </c>
       <c r="H348" s="20">
-        <f>VLOOKUP(G348,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="I348" s="23"/>
@@ -11995,7 +12193,7 @@
         <v>11</v>
       </c>
       <c r="H349" s="20">
-        <f>VLOOKUP(G349,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="I349" s="23"/>
@@ -12026,7 +12224,7 @@
         <v>12</v>
       </c>
       <c r="H350" s="20">
-        <f>VLOOKUP(G350,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="I350" s="23">
@@ -12059,7 +12257,7 @@
         <v>55</v>
       </c>
       <c r="H351" s="20">
-        <f>VLOOKUP(G351,$G$1:$H$222,2,0)</f>
+        <f t="shared" ref="H351:H414" si="2">VLOOKUP(G351,$G$1:$H$222,2,0)</f>
         <v>18</v>
       </c>
       <c r="I351" s="23"/>
@@ -12090,7 +12288,7 @@
         <v>167</v>
       </c>
       <c r="H352" s="20">
-        <f>VLOOKUP(G352,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="I352" s="23"/>
@@ -12121,7 +12319,7 @@
         <v>14</v>
       </c>
       <c r="H353" s="20">
-        <f>VLOOKUP(G353,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="I353" s="23"/>
@@ -12152,7 +12350,7 @@
         <v>15</v>
       </c>
       <c r="H354" s="20">
-        <f>VLOOKUP(G354,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="I354" s="23">
@@ -12185,7 +12383,7 @@
         <v>16</v>
       </c>
       <c r="H355" s="20">
-        <f>VLOOKUP(G355,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="I355" s="23">
@@ -12218,7 +12416,7 @@
         <v>17</v>
       </c>
       <c r="H356" s="20">
-        <f>VLOOKUP(G356,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="I356" s="23">
@@ -12251,7 +12449,7 @@
         <v>18</v>
       </c>
       <c r="H357" s="20">
-        <f>VLOOKUP(G357,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="I357" s="24">
@@ -12284,7 +12482,7 @@
         <v>4</v>
       </c>
       <c r="H358" s="20">
-        <f>VLOOKUP(G358,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="I358" s="21"/>
@@ -12315,7 +12513,7 @@
         <v>5</v>
       </c>
       <c r="H359" s="20">
-        <f>VLOOKUP(G359,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="I359" s="23">
@@ -12348,7 +12546,7 @@
         <v>6</v>
       </c>
       <c r="H360" s="20">
-        <f>VLOOKUP(G360,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="I360" s="23">
@@ -12381,7 +12579,7 @@
         <v>7</v>
       </c>
       <c r="H361" s="20">
-        <f>VLOOKUP(G361,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I361" s="23"/>
@@ -12412,7 +12610,7 @@
         <v>8</v>
       </c>
       <c r="H362" s="20">
-        <f>VLOOKUP(G362,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>49</v>
       </c>
       <c r="I362" s="23">
@@ -12445,7 +12643,7 @@
         <v>9</v>
       </c>
       <c r="H363" s="20">
-        <f>VLOOKUP(G363,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="I363" s="23"/>
@@ -12476,7 +12674,7 @@
         <v>11</v>
       </c>
       <c r="H364" s="20">
-        <f>VLOOKUP(G364,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="I364" s="23">
@@ -12509,7 +12707,7 @@
         <v>12</v>
       </c>
       <c r="H365" s="20">
-        <f>VLOOKUP(G365,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="I365" s="23">
@@ -12542,7 +12740,7 @@
         <v>55</v>
       </c>
       <c r="H366" s="20">
-        <f>VLOOKUP(G366,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="I366" s="23"/>
@@ -12573,7 +12771,7 @@
         <v>167</v>
       </c>
       <c r="H367" s="20">
-        <f>VLOOKUP(G367,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="I367" s="23"/>
@@ -12604,7 +12802,7 @@
         <v>14</v>
       </c>
       <c r="H368" s="20">
-        <f>VLOOKUP(G368,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="I368" s="23"/>
@@ -12635,7 +12833,7 @@
         <v>15</v>
       </c>
       <c r="H369" s="20">
-        <f>VLOOKUP(G369,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="I369" s="23">
@@ -12668,7 +12866,7 @@
         <v>16</v>
       </c>
       <c r="H370" s="20">
-        <f>VLOOKUP(G370,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="I370" s="23">
@@ -12701,7 +12899,7 @@
         <v>17</v>
       </c>
       <c r="H371" s="20">
-        <f>VLOOKUP(G371,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="I371" s="23"/>
@@ -12732,7 +12930,7 @@
         <v>18</v>
       </c>
       <c r="H372" s="20">
-        <f>VLOOKUP(G372,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="I372" s="24"/>
@@ -12763,7 +12961,7 @@
         <v>4</v>
       </c>
       <c r="H373" s="20">
-        <f>VLOOKUP(G373,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="I373" s="21"/>
@@ -12794,7 +12992,7 @@
         <v>5</v>
       </c>
       <c r="H374" s="20">
-        <f>VLOOKUP(G374,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="I374" s="23"/>
@@ -12825,7 +13023,7 @@
         <v>6</v>
       </c>
       <c r="H375" s="20">
-        <f>VLOOKUP(G375,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="I375" s="23"/>
@@ -12856,7 +13054,7 @@
         <v>7</v>
       </c>
       <c r="H376" s="20">
-        <f>VLOOKUP(G376,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I376" s="23"/>
@@ -12887,7 +13085,7 @@
         <v>8</v>
       </c>
       <c r="H377" s="20">
-        <f>VLOOKUP(G377,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>49</v>
       </c>
       <c r="I377" s="23"/>
@@ -12918,7 +13116,7 @@
         <v>9</v>
       </c>
       <c r="H378" s="20">
-        <f>VLOOKUP(G378,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="I378" s="23">
@@ -12951,7 +13149,7 @@
         <v>11</v>
       </c>
       <c r="H379" s="20">
-        <f>VLOOKUP(G379,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="I379" s="23"/>
@@ -12982,7 +13180,7 @@
         <v>12</v>
       </c>
       <c r="H380" s="20">
-        <f>VLOOKUP(G380,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="I380" s="23"/>
@@ -13013,7 +13211,7 @@
         <v>55</v>
       </c>
       <c r="H381" s="20">
-        <f>VLOOKUP(G381,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="I381" s="23"/>
@@ -13044,7 +13242,7 @@
         <v>167</v>
       </c>
       <c r="H382" s="20">
-        <f>VLOOKUP(G382,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="I382" s="23"/>
@@ -13075,7 +13273,7 @@
         <v>14</v>
       </c>
       <c r="H383" s="20">
-        <f>VLOOKUP(G383,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="I383" s="23"/>
@@ -13106,7 +13304,7 @@
         <v>15</v>
       </c>
       <c r="H384" s="20">
-        <f>VLOOKUP(G384,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="I384" s="23"/>
@@ -13137,7 +13335,7 @@
         <v>16</v>
       </c>
       <c r="H385" s="20">
-        <f>VLOOKUP(G385,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="I385" s="23"/>
@@ -13168,7 +13366,7 @@
         <v>17</v>
       </c>
       <c r="H386" s="20">
-        <f>VLOOKUP(G386,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="I386" s="23"/>
@@ -13199,7 +13397,7 @@
         <v>18</v>
       </c>
       <c r="H387" s="20">
-        <f>VLOOKUP(G387,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="I387" s="24"/>
@@ -13230,7 +13428,7 @@
         <v>4</v>
       </c>
       <c r="H388" s="20">
-        <f>VLOOKUP(G388,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="I388" s="21">
@@ -13263,7 +13461,7 @@
         <v>5</v>
       </c>
       <c r="H389" s="20">
-        <f>VLOOKUP(G389,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="I389" s="23">
@@ -13296,7 +13494,7 @@
         <v>6</v>
       </c>
       <c r="H390" s="20">
-        <f>VLOOKUP(G390,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="I390" s="23">
@@ -13329,7 +13527,7 @@
         <v>7</v>
       </c>
       <c r="H391" s="20">
-        <f>VLOOKUP(G391,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I391" s="23">
@@ -13362,7 +13560,7 @@
         <v>8</v>
       </c>
       <c r="H392" s="20">
-        <f>VLOOKUP(G392,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>49</v>
       </c>
       <c r="I392" s="23">
@@ -13395,7 +13593,7 @@
         <v>9</v>
       </c>
       <c r="H393" s="20">
-        <f>VLOOKUP(G393,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="I393" s="23"/>
@@ -13426,7 +13624,7 @@
         <v>11</v>
       </c>
       <c r="H394" s="20">
-        <f>VLOOKUP(G394,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="I394" s="23"/>
@@ -13457,7 +13655,7 @@
         <v>12</v>
       </c>
       <c r="H395" s="20">
-        <f>VLOOKUP(G395,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="I395" s="23">
@@ -13490,7 +13688,7 @@
         <v>55</v>
       </c>
       <c r="H396" s="20">
-        <f>VLOOKUP(G396,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="I396" s="23">
@@ -13523,7 +13721,7 @@
         <v>167</v>
       </c>
       <c r="H397" s="20">
-        <f>VLOOKUP(G397,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="I397" s="23"/>
@@ -13554,7 +13752,7 @@
         <v>14</v>
       </c>
       <c r="H398" s="20">
-        <f>VLOOKUP(G398,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="I398" s="23"/>
@@ -13585,7 +13783,7 @@
         <v>15</v>
       </c>
       <c r="H399" s="20">
-        <f>VLOOKUP(G399,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="I399" s="23">
@@ -13618,7 +13816,7 @@
         <v>16</v>
       </c>
       <c r="H400" s="20">
-        <f>VLOOKUP(G400,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="I400" s="23">
@@ -13651,7 +13849,7 @@
         <v>17</v>
       </c>
       <c r="H401" s="20">
-        <f>VLOOKUP(G401,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="I401" s="23"/>
@@ -13682,7 +13880,7 @@
         <v>18</v>
       </c>
       <c r="H402" s="20">
-        <f>VLOOKUP(G402,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="I402" s="24">
@@ -13715,7 +13913,7 @@
         <v>4</v>
       </c>
       <c r="H403" s="20">
-        <f>VLOOKUP(G403,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="I403" s="21">
@@ -13748,7 +13946,7 @@
         <v>5</v>
       </c>
       <c r="H404" s="20">
-        <f>VLOOKUP(G404,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="I404" s="23">
@@ -13781,7 +13979,7 @@
         <v>6</v>
       </c>
       <c r="H405" s="20">
-        <f>VLOOKUP(G405,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="I405" s="23">
@@ -13814,7 +14012,7 @@
         <v>7</v>
       </c>
       <c r="H406" s="20">
-        <f>VLOOKUP(G406,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="I406" s="23"/>
@@ -13845,7 +14043,7 @@
         <v>8</v>
       </c>
       <c r="H407" s="20">
-        <f>VLOOKUP(G407,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>49</v>
       </c>
       <c r="I407" s="23">
@@ -13878,7 +14076,7 @@
         <v>9</v>
       </c>
       <c r="H408" s="20">
-        <f>VLOOKUP(G408,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="I408" s="23"/>
@@ -13909,7 +14107,7 @@
         <v>11</v>
       </c>
       <c r="H409" s="20">
-        <f>VLOOKUP(G409,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="I409" s="23"/>
@@ -13940,7 +14138,7 @@
         <v>12</v>
       </c>
       <c r="H410" s="20">
-        <f>VLOOKUP(G410,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="I410" s="23">
@@ -13973,7 +14171,7 @@
         <v>55</v>
       </c>
       <c r="H411" s="20">
-        <f>VLOOKUP(G411,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="I411" s="23"/>
@@ -14004,7 +14202,7 @@
         <v>167</v>
       </c>
       <c r="H412" s="20">
-        <f>VLOOKUP(G412,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="I412" s="23"/>
@@ -14035,7 +14233,7 @@
         <v>14</v>
       </c>
       <c r="H413" s="20">
-        <f>VLOOKUP(G413,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="I413" s="23"/>
@@ -14066,7 +14264,7 @@
         <v>15</v>
       </c>
       <c r="H414" s="20">
-        <f>VLOOKUP(G414,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="I414" s="23">
@@ -14099,7 +14297,7 @@
         <v>16</v>
       </c>
       <c r="H415" s="20">
-        <f>VLOOKUP(G415,$G$1:$H$222,2,0)</f>
+        <f t="shared" ref="H415:H478" si="3">VLOOKUP(G415,$G$1:$H$222,2,0)</f>
         <v>23</v>
       </c>
       <c r="I415" s="23">
@@ -14132,7 +14330,7 @@
         <v>17</v>
       </c>
       <c r="H416" s="20">
-        <f>VLOOKUP(G416,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="I416" s="23"/>
@@ -14163,7 +14361,7 @@
         <v>18</v>
       </c>
       <c r="H417" s="20">
-        <f>VLOOKUP(G417,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="I417" s="24"/>
@@ -14194,7 +14392,7 @@
         <v>4</v>
       </c>
       <c r="H418" s="20">
-        <f>VLOOKUP(G418,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="I418" s="21"/>
@@ -14225,7 +14423,7 @@
         <v>5</v>
       </c>
       <c r="H419" s="20">
-        <f>VLOOKUP(G419,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="I419" s="23">
@@ -14258,7 +14456,7 @@
         <v>6</v>
       </c>
       <c r="H420" s="20">
-        <f>VLOOKUP(G420,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="I420" s="23">
@@ -14291,7 +14489,7 @@
         <v>7</v>
       </c>
       <c r="H421" s="20">
-        <f>VLOOKUP(G421,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="I421" s="23">
@@ -14324,7 +14522,7 @@
         <v>8</v>
       </c>
       <c r="H422" s="20">
-        <f>VLOOKUP(G422,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>49</v>
       </c>
       <c r="I422" s="23">
@@ -14357,7 +14555,7 @@
         <v>9</v>
       </c>
       <c r="H423" s="20">
-        <f>VLOOKUP(G423,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="I423" s="23"/>
@@ -14388,7 +14586,7 @@
         <v>11</v>
       </c>
       <c r="H424" s="20">
-        <f>VLOOKUP(G424,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="I424" s="23"/>
@@ -14419,7 +14617,7 @@
         <v>12</v>
       </c>
       <c r="H425" s="20">
-        <f>VLOOKUP(G425,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="I425" s="23">
@@ -14452,7 +14650,7 @@
         <v>55</v>
       </c>
       <c r="H426" s="20">
-        <f>VLOOKUP(G426,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="I426" s="23"/>
@@ -14483,7 +14681,7 @@
         <v>167</v>
       </c>
       <c r="H427" s="20">
-        <f>VLOOKUP(G427,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="I427" s="23"/>
@@ -14514,7 +14712,7 @@
         <v>14</v>
       </c>
       <c r="H428" s="20">
-        <f>VLOOKUP(G428,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="I428" s="23"/>
@@ -14545,7 +14743,7 @@
         <v>15</v>
       </c>
       <c r="H429" s="20">
-        <f>VLOOKUP(G429,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="I429" s="23">
@@ -14578,7 +14776,7 @@
         <v>16</v>
       </c>
       <c r="H430" s="20">
-        <f>VLOOKUP(G430,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="I430" s="23">
@@ -14611,7 +14809,7 @@
         <v>17</v>
       </c>
       <c r="H431" s="20">
-        <f>VLOOKUP(G431,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="I431" s="23"/>
@@ -14642,7 +14840,7 @@
         <v>18</v>
       </c>
       <c r="H432" s="20">
-        <f>VLOOKUP(G432,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="I432" s="24">
@@ -14675,7 +14873,7 @@
         <v>4</v>
       </c>
       <c r="H433" s="20">
-        <f>VLOOKUP(G433,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="I433" s="21"/>
@@ -14706,7 +14904,7 @@
         <v>5</v>
       </c>
       <c r="H434" s="20">
-        <f>VLOOKUP(G434,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="I434" s="23"/>
@@ -14737,7 +14935,7 @@
         <v>6</v>
       </c>
       <c r="H435" s="20">
-        <f>VLOOKUP(G435,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="I435" s="23"/>
@@ -14768,7 +14966,7 @@
         <v>7</v>
       </c>
       <c r="H436" s="20">
-        <f>VLOOKUP(G436,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="I436" s="23"/>
@@ -14799,7 +14997,7 @@
         <v>8</v>
       </c>
       <c r="H437" s="20">
-        <f>VLOOKUP(G437,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>49</v>
       </c>
       <c r="I437" s="23">
@@ -14832,7 +15030,7 @@
         <v>9</v>
       </c>
       <c r="H438" s="20">
-        <f>VLOOKUP(G438,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="I438" s="23"/>
@@ -14863,7 +15061,7 @@
         <v>11</v>
       </c>
       <c r="H439" s="20">
-        <f>VLOOKUP(G439,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="I439" s="23">
@@ -14896,7 +15094,7 @@
         <v>12</v>
       </c>
       <c r="H440" s="20">
-        <f>VLOOKUP(G440,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="I440" s="23">
@@ -14929,7 +15127,7 @@
         <v>55</v>
       </c>
       <c r="H441" s="20">
-        <f>VLOOKUP(G441,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="I441" s="23">
@@ -14962,7 +15160,7 @@
         <v>167</v>
       </c>
       <c r="H442" s="20">
-        <f>VLOOKUP(G442,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="I442" s="23"/>
@@ -14993,7 +15191,7 @@
         <v>14</v>
       </c>
       <c r="H443" s="20">
-        <f>VLOOKUP(G443,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="I443" s="23"/>
@@ -15024,7 +15222,7 @@
         <v>15</v>
       </c>
       <c r="H444" s="20">
-        <f>VLOOKUP(G444,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="I444" s="23">
@@ -15057,7 +15255,7 @@
         <v>16</v>
       </c>
       <c r="H445" s="20">
-        <f>VLOOKUP(G445,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="I445" s="23">
@@ -15090,7 +15288,7 @@
         <v>17</v>
       </c>
       <c r="H446" s="20">
-        <f>VLOOKUP(G446,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="I446" s="23"/>
@@ -15121,7 +15319,7 @@
         <v>18</v>
       </c>
       <c r="H447" s="20">
-        <f>VLOOKUP(G447,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="I447" s="24"/>
@@ -15152,7 +15350,7 @@
         <v>4</v>
       </c>
       <c r="H448" s="20">
-        <f>VLOOKUP(G448,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="I448" s="21">
@@ -15185,7 +15383,7 @@
         <v>5</v>
       </c>
       <c r="H449" s="20">
-        <f>VLOOKUP(G449,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="I449" s="23">
@@ -15218,7 +15416,7 @@
         <v>6</v>
       </c>
       <c r="H450" s="20">
-        <f>VLOOKUP(G450,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="I450" s="23">
@@ -15251,7 +15449,7 @@
         <v>7</v>
       </c>
       <c r="H451" s="20">
-        <f>VLOOKUP(G451,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="I451" s="23"/>
@@ -15282,7 +15480,7 @@
         <v>8</v>
       </c>
       <c r="H452" s="20">
-        <f>VLOOKUP(G452,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>49</v>
       </c>
       <c r="I452" s="23">
@@ -15315,7 +15513,7 @@
         <v>9</v>
       </c>
       <c r="H453" s="20">
-        <f>VLOOKUP(G453,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="I453" s="23"/>
@@ -15346,7 +15544,7 @@
         <v>11</v>
       </c>
       <c r="H454" s="20">
-        <f>VLOOKUP(G454,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="I454" s="23"/>
@@ -15377,7 +15575,7 @@
         <v>12</v>
       </c>
       <c r="H455" s="20">
-        <f>VLOOKUP(G455,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="I455" s="23">
@@ -15410,7 +15608,7 @@
         <v>55</v>
       </c>
       <c r="H456" s="20">
-        <f>VLOOKUP(G456,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="I456" s="23">
@@ -15443,7 +15641,7 @@
         <v>167</v>
       </c>
       <c r="H457" s="20">
-        <f>VLOOKUP(G457,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="I457" s="23"/>
@@ -15474,7 +15672,7 @@
         <v>14</v>
       </c>
       <c r="H458" s="20">
-        <f>VLOOKUP(G458,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="I458" s="23"/>
@@ -15505,7 +15703,7 @@
         <v>15</v>
       </c>
       <c r="H459" s="20">
-        <f>VLOOKUP(G459,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="I459" s="23">
@@ -15538,7 +15736,7 @@
         <v>16</v>
       </c>
       <c r="H460" s="20">
-        <f>VLOOKUP(G460,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="I460" s="23">
@@ -15571,7 +15769,7 @@
         <v>17</v>
       </c>
       <c r="H461" s="20">
-        <f>VLOOKUP(G461,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="I461" s="23"/>
@@ -15602,7 +15800,7 @@
         <v>18</v>
       </c>
       <c r="H462" s="20">
-        <f>VLOOKUP(G462,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="I462" s="24">
@@ -15635,7 +15833,7 @@
         <v>4</v>
       </c>
       <c r="H463" s="20">
-        <f>VLOOKUP(G463,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="I463" s="21">
@@ -15668,7 +15866,7 @@
         <v>5</v>
       </c>
       <c r="H464" s="20">
-        <f>VLOOKUP(G464,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="I464" s="23"/>
@@ -15699,7 +15897,7 @@
         <v>6</v>
       </c>
       <c r="H465" s="20">
-        <f>VLOOKUP(G465,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="I465" s="23">
@@ -15732,7 +15930,7 @@
         <v>7</v>
       </c>
       <c r="H466" s="20">
-        <f>VLOOKUP(G466,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="I466" s="23"/>
@@ -15763,7 +15961,7 @@
         <v>8</v>
       </c>
       <c r="H467" s="20">
-        <f>VLOOKUP(G467,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>49</v>
       </c>
       <c r="I467" s="23"/>
@@ -15794,7 +15992,7 @@
         <v>9</v>
       </c>
       <c r="H468" s="20">
-        <f>VLOOKUP(G468,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="I468" s="23"/>
@@ -15825,7 +16023,7 @@
         <v>11</v>
       </c>
       <c r="H469" s="20">
-        <f>VLOOKUP(G469,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="I469" s="23"/>
@@ -15856,7 +16054,7 @@
         <v>12</v>
       </c>
       <c r="H470" s="20">
-        <f>VLOOKUP(G470,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="I470" s="23">
@@ -15889,7 +16087,7 @@
         <v>55</v>
       </c>
       <c r="H471" s="20">
-        <f>VLOOKUP(G471,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="I471" s="23">
@@ -15922,7 +16120,7 @@
         <v>167</v>
       </c>
       <c r="H472" s="20">
-        <f>VLOOKUP(G472,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="I472" s="23"/>
@@ -15953,7 +16151,7 @@
         <v>14</v>
       </c>
       <c r="H473" s="20">
-        <f>VLOOKUP(G473,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="I473" s="23"/>
@@ -15984,7 +16182,7 @@
         <v>15</v>
       </c>
       <c r="H474" s="20">
-        <f>VLOOKUP(G474,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="I474" s="23">
@@ -16017,7 +16215,7 @@
         <v>16</v>
       </c>
       <c r="H475" s="20">
-        <f>VLOOKUP(G475,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="I475" s="23">
@@ -16050,7 +16248,7 @@
         <v>17</v>
       </c>
       <c r="H476" s="20">
-        <f>VLOOKUP(G476,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="I476" s="23"/>
@@ -16081,7 +16279,7 @@
         <v>18</v>
       </c>
       <c r="H477" s="20">
-        <f>VLOOKUP(G477,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="I477" s="24"/>
@@ -16112,7 +16310,7 @@
         <v>4</v>
       </c>
       <c r="H478" s="20">
-        <f>VLOOKUP(G478,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="I478" s="21">
@@ -16145,7 +16343,7 @@
         <v>5</v>
       </c>
       <c r="H479" s="20">
-        <f>VLOOKUP(G479,$G$1:$H$222,2,0)</f>
+        <f t="shared" ref="H479:H542" si="4">VLOOKUP(G479,$G$1:$H$222,2,0)</f>
         <v>19</v>
       </c>
       <c r="I479" s="23"/>
@@ -16176,7 +16374,7 @@
         <v>6</v>
       </c>
       <c r="H480" s="20">
-        <f>VLOOKUP(G480,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="I480" s="23"/>
@@ -16207,7 +16405,7 @@
         <v>7</v>
       </c>
       <c r="H481" s="20">
-        <f>VLOOKUP(G481,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="I481" s="23"/>
@@ -16238,7 +16436,7 @@
         <v>8</v>
       </c>
       <c r="H482" s="20">
-        <f>VLOOKUP(G482,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>49</v>
       </c>
       <c r="I482" s="23">
@@ -16271,7 +16469,7 @@
         <v>9</v>
       </c>
       <c r="H483" s="20">
-        <f>VLOOKUP(G483,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="I483" s="23"/>
@@ -16302,7 +16500,7 @@
         <v>11</v>
       </c>
       <c r="H484" s="20">
-        <f>VLOOKUP(G484,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="I484" s="23"/>
@@ -16333,7 +16531,7 @@
         <v>12</v>
       </c>
       <c r="H485" s="20">
-        <f>VLOOKUP(G485,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="I485" s="23">
@@ -16366,7 +16564,7 @@
         <v>55</v>
       </c>
       <c r="H486" s="20">
-        <f>VLOOKUP(G486,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="I486" s="23"/>
@@ -16397,7 +16595,7 @@
         <v>167</v>
       </c>
       <c r="H487" s="20">
-        <f>VLOOKUP(G487,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="I487" s="23"/>
@@ -16428,7 +16626,7 @@
         <v>14</v>
       </c>
       <c r="H488" s="20">
-        <f>VLOOKUP(G488,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>27</v>
       </c>
       <c r="I488" s="23"/>
@@ -16459,7 +16657,7 @@
         <v>15</v>
       </c>
       <c r="H489" s="20">
-        <f>VLOOKUP(G489,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
       <c r="I489" s="23">
@@ -16492,7 +16690,7 @@
         <v>16</v>
       </c>
       <c r="H490" s="20">
-        <f>VLOOKUP(G490,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="I490" s="23">
@@ -16525,7 +16723,7 @@
         <v>17</v>
       </c>
       <c r="H491" s="20">
-        <f>VLOOKUP(G491,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="I491" s="23"/>
@@ -16556,7 +16754,7 @@
         <v>18</v>
       </c>
       <c r="H492" s="20">
-        <f>VLOOKUP(G492,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>50</v>
       </c>
       <c r="I492" s="24"/>
@@ -16587,7 +16785,7 @@
         <v>4</v>
       </c>
       <c r="H493" s="20">
-        <f>VLOOKUP(G493,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
       <c r="I493" s="21">
@@ -16620,7 +16818,7 @@
         <v>5</v>
       </c>
       <c r="H494" s="20">
-        <f>VLOOKUP(G494,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="I494" s="23">
@@ -16653,7 +16851,7 @@
         <v>6</v>
       </c>
       <c r="H495" s="20">
-        <f>VLOOKUP(G495,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="I495" s="23">
@@ -16686,7 +16884,7 @@
         <v>7</v>
       </c>
       <c r="H496" s="20">
-        <f>VLOOKUP(G496,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="I496" s="23">
@@ -16719,7 +16917,7 @@
         <v>8</v>
       </c>
       <c r="H497" s="20">
-        <f>VLOOKUP(G497,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>49</v>
       </c>
       <c r="I497" s="23">
@@ -16752,7 +16950,7 @@
         <v>9</v>
       </c>
       <c r="H498" s="20">
-        <f>VLOOKUP(G498,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="I498" s="23"/>
@@ -16783,7 +16981,7 @@
         <v>11</v>
       </c>
       <c r="H499" s="20">
-        <f>VLOOKUP(G499,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="I499" s="23"/>
@@ -16814,7 +17012,7 @@
         <v>12</v>
       </c>
       <c r="H500" s="20">
-        <f>VLOOKUP(G500,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="I500" s="23">
@@ -16847,7 +17045,7 @@
         <v>55</v>
       </c>
       <c r="H501" s="20">
-        <f>VLOOKUP(G501,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="I501" s="23"/>
@@ -16878,7 +17076,7 @@
         <v>167</v>
       </c>
       <c r="H502" s="20">
-        <f>VLOOKUP(G502,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="I502" s="23"/>
@@ -16909,7 +17107,7 @@
         <v>14</v>
       </c>
       <c r="H503" s="20">
-        <f>VLOOKUP(G503,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>27</v>
       </c>
       <c r="I503" s="23">
@@ -16942,7 +17140,7 @@
         <v>15</v>
       </c>
       <c r="H504" s="20">
-        <f>VLOOKUP(G504,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
       <c r="I504" s="23">
@@ -16975,7 +17173,7 @@
         <v>16</v>
       </c>
       <c r="H505" s="20">
-        <f>VLOOKUP(G505,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="I505" s="23">
@@ -17008,7 +17206,7 @@
         <v>17</v>
       </c>
       <c r="H506" s="20">
-        <f>VLOOKUP(G506,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="I506" s="23"/>
@@ -17039,7 +17237,7 @@
         <v>18</v>
       </c>
       <c r="H507" s="20">
-        <f>VLOOKUP(G507,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>50</v>
       </c>
       <c r="I507" s="24">
@@ -17065,11 +17263,14 @@
       <c r="E508" s="25" t="s">
         <v>180</v>
       </c>
+      <c r="F508">
+        <v>1453</v>
+      </c>
       <c r="G508" s="19" t="s">
         <v>4</v>
       </c>
       <c r="H508" s="20">
-        <f>VLOOKUP(G508,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
       <c r="I508" s="21">
@@ -17095,11 +17296,14 @@
       <c r="E509" s="25" t="s">
         <v>180</v>
       </c>
+      <c r="F509">
+        <v>1453</v>
+      </c>
       <c r="G509" s="22" t="s">
         <v>5</v>
       </c>
       <c r="H509" s="20">
-        <f>VLOOKUP(G509,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="I509" s="23">
@@ -17125,11 +17329,14 @@
       <c r="E510" s="25" t="s">
         <v>180</v>
       </c>
+      <c r="F510">
+        <v>1453</v>
+      </c>
       <c r="G510" s="22" t="s">
         <v>6</v>
       </c>
       <c r="H510" s="20">
-        <f>VLOOKUP(G510,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="I510" s="23">
@@ -17155,11 +17362,14 @@
       <c r="E511" s="25" t="s">
         <v>180</v>
       </c>
+      <c r="F511">
+        <v>1453</v>
+      </c>
       <c r="G511" s="22" t="s">
         <v>7</v>
       </c>
       <c r="H511" s="20">
-        <f>VLOOKUP(G511,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="I511" s="23">
@@ -17185,11 +17395,14 @@
       <c r="E512" s="25" t="s">
         <v>180</v>
       </c>
+      <c r="F512">
+        <v>1453</v>
+      </c>
       <c r="G512" s="22" t="s">
         <v>8</v>
       </c>
       <c r="H512" s="20">
-        <f>VLOOKUP(G512,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>49</v>
       </c>
       <c r="I512" s="23">
@@ -17215,11 +17428,14 @@
       <c r="E513" s="25" t="s">
         <v>180</v>
       </c>
+      <c r="F513">
+        <v>1453</v>
+      </c>
       <c r="G513" s="22" t="s">
         <v>9</v>
       </c>
       <c r="H513" s="20">
-        <f>VLOOKUP(G513,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="I513" s="23"/>
@@ -17243,11 +17459,14 @@
       <c r="E514" s="25" t="s">
         <v>180</v>
       </c>
+      <c r="F514">
+        <v>1453</v>
+      </c>
       <c r="G514" s="22" t="s">
         <v>11</v>
       </c>
       <c r="H514" s="20">
-        <f>VLOOKUP(G514,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="I514" s="23">
@@ -17273,11 +17492,14 @@
       <c r="E515" s="25" t="s">
         <v>180</v>
       </c>
+      <c r="F515">
+        <v>1453</v>
+      </c>
       <c r="G515" s="22" t="s">
         <v>12</v>
       </c>
       <c r="H515" s="20">
-        <f>VLOOKUP(G515,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="I515" s="23">
@@ -17303,11 +17525,14 @@
       <c r="E516" s="25" t="s">
         <v>180</v>
       </c>
+      <c r="F516">
+        <v>1453</v>
+      </c>
       <c r="G516" s="22" t="s">
         <v>55</v>
       </c>
       <c r="H516" s="20">
-        <f>VLOOKUP(G516,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="I516" s="23">
@@ -17333,11 +17558,14 @@
       <c r="E517" s="25" t="s">
         <v>180</v>
       </c>
+      <c r="F517">
+        <v>1453</v>
+      </c>
       <c r="G517" s="22" t="s">
         <v>167</v>
       </c>
       <c r="H517" s="20">
-        <f>VLOOKUP(G517,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="I517" s="23"/>
@@ -17361,11 +17589,14 @@
       <c r="E518" s="25" t="s">
         <v>180</v>
       </c>
+      <c r="F518">
+        <v>1453</v>
+      </c>
       <c r="G518" s="22" t="s">
         <v>14</v>
       </c>
       <c r="H518" s="20">
-        <f>VLOOKUP(G518,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>27</v>
       </c>
       <c r="I518" s="23">
@@ -17391,11 +17622,14 @@
       <c r="E519" s="25" t="s">
         <v>180</v>
       </c>
+      <c r="F519">
+        <v>1453</v>
+      </c>
       <c r="G519" s="22" t="s">
         <v>15</v>
       </c>
       <c r="H519" s="20">
-        <f>VLOOKUP(G519,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
       <c r="I519" s="23">
@@ -17421,11 +17655,14 @@
       <c r="E520" s="25" t="s">
         <v>180</v>
       </c>
+      <c r="F520">
+        <v>1453</v>
+      </c>
       <c r="G520" s="22" t="s">
         <v>16</v>
       </c>
       <c r="H520" s="20">
-        <f>VLOOKUP(G520,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="I520" s="23">
@@ -17451,11 +17688,14 @@
       <c r="E521" s="25" t="s">
         <v>180</v>
       </c>
+      <c r="F521">
+        <v>1453</v>
+      </c>
       <c r="G521" s="22" t="s">
         <v>17</v>
       </c>
       <c r="H521" s="20">
-        <f>VLOOKUP(G521,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="I521" s="23"/>
@@ -17479,11 +17719,14 @@
       <c r="E522" s="25" t="s">
         <v>180</v>
       </c>
+      <c r="F522">
+        <v>1453</v>
+      </c>
       <c r="G522" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H522" s="20">
-        <f>VLOOKUP(G522,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>50</v>
       </c>
       <c r="I522" s="24"/>
@@ -17507,11 +17750,14 @@
       <c r="E523" s="26" t="s">
         <v>181</v>
       </c>
+      <c r="F523">
+        <v>1455</v>
+      </c>
       <c r="G523" s="19" t="s">
         <v>4</v>
       </c>
       <c r="H523" s="20">
-        <f>VLOOKUP(G523,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
       <c r="I523" s="21"/>
@@ -17535,11 +17781,14 @@
       <c r="E524" s="26" t="s">
         <v>181</v>
       </c>
+      <c r="F524">
+        <v>1455</v>
+      </c>
       <c r="G524" s="22" t="s">
         <v>5</v>
       </c>
       <c r="H524" s="20">
-        <f>VLOOKUP(G524,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="I524" s="23">
@@ -17565,11 +17814,14 @@
       <c r="E525" s="26" t="s">
         <v>181</v>
       </c>
+      <c r="F525">
+        <v>1455</v>
+      </c>
       <c r="G525" s="22" t="s">
         <v>6</v>
       </c>
       <c r="H525" s="20">
-        <f>VLOOKUP(G525,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="I525" s="23"/>
@@ -17593,11 +17845,14 @@
       <c r="E526" s="26" t="s">
         <v>181</v>
       </c>
+      <c r="F526">
+        <v>1455</v>
+      </c>
       <c r="G526" s="22" t="s">
         <v>7</v>
       </c>
       <c r="H526" s="20">
-        <f>VLOOKUP(G526,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="I526" s="23"/>
@@ -17621,11 +17876,14 @@
       <c r="E527" s="26" t="s">
         <v>181</v>
       </c>
+      <c r="F527">
+        <v>1455</v>
+      </c>
       <c r="G527" s="22" t="s">
         <v>8</v>
       </c>
       <c r="H527" s="20">
-        <f>VLOOKUP(G527,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>49</v>
       </c>
       <c r="I527" s="23">
@@ -17651,11 +17909,14 @@
       <c r="E528" s="26" t="s">
         <v>181</v>
       </c>
+      <c r="F528">
+        <v>1455</v>
+      </c>
       <c r="G528" s="22" t="s">
         <v>9</v>
       </c>
       <c r="H528" s="20">
-        <f>VLOOKUP(G528,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="I528" s="23">
@@ -17681,11 +17942,14 @@
       <c r="E529" s="26" t="s">
         <v>181</v>
       </c>
+      <c r="F529">
+        <v>1455</v>
+      </c>
       <c r="G529" s="22" t="s">
         <v>11</v>
       </c>
       <c r="H529" s="20">
-        <f>VLOOKUP(G529,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="I529" s="23"/>
@@ -17709,11 +17973,14 @@
       <c r="E530" s="26" t="s">
         <v>181</v>
       </c>
+      <c r="F530">
+        <v>1455</v>
+      </c>
       <c r="G530" s="22" t="s">
         <v>12</v>
       </c>
       <c r="H530" s="20">
-        <f>VLOOKUP(G530,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="I530" s="23">
@@ -17739,11 +18006,14 @@
       <c r="E531" s="26" t="s">
         <v>181</v>
       </c>
+      <c r="F531">
+        <v>1455</v>
+      </c>
       <c r="G531" s="22" t="s">
         <v>55</v>
       </c>
       <c r="H531" s="20">
-        <f>VLOOKUP(G531,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="I531" s="23"/>
@@ -17767,11 +18037,14 @@
       <c r="E532" s="26" t="s">
         <v>181</v>
       </c>
+      <c r="F532">
+        <v>1455</v>
+      </c>
       <c r="G532" s="22" t="s">
         <v>167</v>
       </c>
       <c r="H532" s="20">
-        <f>VLOOKUP(G532,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="I532" s="23"/>
@@ -17795,11 +18068,14 @@
       <c r="E533" s="26" t="s">
         <v>181</v>
       </c>
+      <c r="F533">
+        <v>1455</v>
+      </c>
       <c r="G533" s="22" t="s">
         <v>14</v>
       </c>
       <c r="H533" s="20">
-        <f>VLOOKUP(G533,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>27</v>
       </c>
       <c r="I533" s="23"/>
@@ -17823,11 +18099,14 @@
       <c r="E534" s="26" t="s">
         <v>181</v>
       </c>
+      <c r="F534">
+        <v>1455</v>
+      </c>
       <c r="G534" s="22" t="s">
         <v>15</v>
       </c>
       <c r="H534" s="20">
-        <f>VLOOKUP(G534,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
       <c r="I534" s="23">
@@ -17853,11 +18132,14 @@
       <c r="E535" s="26" t="s">
         <v>181</v>
       </c>
+      <c r="F535">
+        <v>1455</v>
+      </c>
       <c r="G535" s="22" t="s">
         <v>16</v>
       </c>
       <c r="H535" s="20">
-        <f>VLOOKUP(G535,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="I535" s="23">
@@ -17883,11 +18165,14 @@
       <c r="E536" s="26" t="s">
         <v>181</v>
       </c>
+      <c r="F536">
+        <v>1455</v>
+      </c>
       <c r="G536" s="22" t="s">
         <v>17</v>
       </c>
       <c r="H536" s="20">
-        <f>VLOOKUP(G536,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="I536" s="23"/>
@@ -17911,11 +18196,14 @@
       <c r="E537" s="26" t="s">
         <v>181</v>
       </c>
+      <c r="F537">
+        <v>1455</v>
+      </c>
       <c r="G537" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H537" s="20">
-        <f>VLOOKUP(G537,$G$1:$H$222,2,0)</f>
+        <f t="shared" si="4"/>
         <v>50</v>
       </c>
       <c r="I537" s="24"/>
@@ -17924,6 +18212,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J537" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
